--- a/MCA/CA2102_Specifications.xlsx
+++ b/MCA/CA2102_Specifications.xlsx
@@ -19378,6 +19378,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>